--- a/exports/trend_1d/COALINDIA_full_report.xlsx
+++ b/exports/trend_1d/COALINDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.77</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42033</v>
+        <v>42034</v>
       </c>
       <c r="H2" t="n">
-        <v>349.05</v>
+        <v>335.95</v>
       </c>
       <c r="I2" t="n">
         <v>341.871853162</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>1.76</v>
+        <v>-2.06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.73</v>
+        <v>2.29</v>
       </c>
       <c r="M2" t="n">
         <v>4.88</v>
       </c>
       <c r="N2" t="n">
-        <v>3.06</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.45</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.65</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42061</v>
+        <v>42062</v>
       </c>
       <c r="H3" t="n">
-        <v>357.8</v>
+        <v>367.95</v>
       </c>
       <c r="I3" t="n">
         <v>360.2860201763706</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.5</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>8.140000000000001</v>
+        <v>10.28</v>
       </c>
       <c r="M3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
         <v>-3.75</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.23</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42068</v>
+        <v>42072</v>
       </c>
       <c r="H4" t="n">
-        <v>338.8</v>
+        <v>332.65</v>
       </c>
       <c r="I4" t="n">
         <v>337.679228548761</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.92</v>
+        <v>-9.59</v>
       </c>
       <c r="L4" t="n">
-        <v>8.43</v>
+        <v>9.91</v>
       </c>
       <c r="M4" t="n">
         <v>5.39</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>11.14</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42101</v>
+        <v>42102</v>
       </c>
       <c r="H5" t="n">
-        <v>334.8</v>
+        <v>354.05</v>
       </c>
       <c r="I5" t="n">
         <v>351.2648368164502</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.65</v>
+        <v>-6.43</v>
       </c>
       <c r="L5" t="n">
-        <v>4.39</v>
+        <v>7.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.99</v>
+        <v>1.57</v>
       </c>
       <c r="N5" t="n">
-        <v>3.74</v>
+        <v>5.75</v>
       </c>
       <c r="O5" t="n">
         <v>-1.82</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="H6" t="n">
-        <v>339.2</v>
+        <v>328.7</v>
       </c>
       <c r="I6" t="n">
         <v>335.6194294153157</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.19</v>
+        <v>-7.16</v>
       </c>
       <c r="L6" t="n">
-        <v>5.55</v>
+        <v>7.41</v>
       </c>
       <c r="M6" t="n">
         <v>0.79</v>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
         <v>5.75</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H7" t="n">
-        <v>356.9</v>
+        <v>364.05</v>
       </c>
       <c r="I7" t="n">
         <v>357.8364072752713</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.58</v>
+        <v>-10.75</v>
       </c>
       <c r="L7" t="n">
-        <v>9.890000000000001</v>
+        <v>11.52</v>
       </c>
       <c r="M7" t="n">
         <v>0.75</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.07</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42223</v>
+        <v>42226</v>
       </c>
       <c r="H8" t="n">
-        <v>386.05</v>
+        <v>379.75</v>
       </c>
       <c r="I8" t="n">
         <v>383.0583807936827</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K8" t="n">
-        <v>6.04</v>
+        <v>4.31</v>
       </c>
       <c r="L8" t="n">
         <v>2.58</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H9" t="n">
-        <v>319</v>
+        <v>322.3</v>
       </c>
       <c r="I9" t="n">
         <v>320.5801084081128</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>15.13</v>
       </c>
       <c r="L9" t="n">
         <v>2.48</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.38</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H10" t="n">
-        <v>296.05</v>
+        <v>286.35</v>
       </c>
       <c r="I10" t="n">
         <v>294.9330312562926</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.140000000000001</v>
+        <v>-11.15</v>
       </c>
       <c r="L10" t="n">
-        <v>8.58</v>
+        <v>11.6</v>
       </c>
       <c r="M10" t="n">
         <v>2.1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>11.85</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42398.38541666666</v>
+        <v>42401.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>297.85</v>
+        <v>305.85</v>
       </c>
       <c r="I11" t="n">
         <v>303.7957349203181</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.38541666666666</v>
+        <v>54.38541666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.02</v>
+        <v>-6.81</v>
       </c>
       <c r="L11" t="n">
         <v>9.59</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.4</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42452.38541666666</v>
+        <v>42457.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>277.45</v>
+        <v>273.25</v>
       </c>
       <c r="I12" t="n">
         <v>273.5323411644986</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.289999999999999</v>
+        <v>-10.66</v>
       </c>
       <c r="L12" t="n">
         <v>11.12</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42521.38541666666</v>
+        <v>42522.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>271.25</v>
+        <v>276.65</v>
       </c>
       <c r="I13" t="n">
         <v>272.984068432277</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K13" t="n">
-        <v>0.73</v>
+        <v>-1.24</v>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="M13" t="n">
         <v>2.83</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.13</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42627.38541666666</v>
+        <v>42628.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>301.95</v>
+        <v>301.4</v>
       </c>
       <c r="I14" t="n">
         <v>301.6555744695939</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K14" t="n">
-        <v>9.15</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>2.75</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.59</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42671.38541666666</v>
+        <v>42675.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>302.35</v>
+        <v>307.25</v>
       </c>
       <c r="I15" t="n">
         <v>305.5494193228952</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="L15" t="n">
         <v>4.15</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.44</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42690.38541666666</v>
+        <v>42691.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>291.4</v>
+        <v>285.65</v>
       </c>
       <c r="I16" t="n">
         <v>288.1610269644532</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.16</v>
+        <v>-7.03</v>
       </c>
       <c r="L16" t="n">
         <v>12.35</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42737.38541666666</v>
+        <v>42738.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>279.35</v>
+        <v>284.2</v>
       </c>
       <c r="I17" t="n">
         <v>282.3111930418282</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K17" t="n">
-        <v>2.21</v>
+        <v>0.51</v>
       </c>
       <c r="L17" t="n">
         <v>2.35</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>6.99</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42804.38541666666</v>
+        <v>42808.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>294.45</v>
+        <v>274.55</v>
       </c>
       <c r="I18" t="n">
         <v>287.6633692243688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K18" t="n">
-        <v>3.61</v>
+        <v>-3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>3.73</v>
       </c>
       <c r="M18" t="n">
-        <v>1.99</v>
+        <v>4.52</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
         <v>1.74</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.98</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42923.38541666666</v>
+        <v>42926.43333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>233.75</v>
+        <v>240.9</v>
       </c>
       <c r="I19" t="n">
         <v>238.0825027072883</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>115</v>
+        <v>118.0479166666667</v>
       </c>
       <c r="K19" t="n">
-        <v>14.86</v>
+        <v>12.26</v>
       </c>
       <c r="L19" t="n">
         <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>3.06</v>
       </c>
       <c r="O19" t="n">
         <v>-6.76</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.39</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42949.38541666666</v>
+        <v>42950.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>233.5</v>
+        <v>225.05</v>
       </c>
       <c r="I20" t="n">
         <v>229.8599301394742</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22.95208333333333</v>
+        <v>23.95208333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.07</v>
+        <v>-6.58</v>
       </c>
       <c r="L20" t="n">
-        <v>5.04</v>
+        <v>6.83</v>
       </c>
       <c r="M20" t="n">
         <v>0.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>3.62</v>
       </c>
       <c r="O20" t="n">
         <v>3.06</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42983.38541666666</v>
+        <v>42984.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>236.3</v>
+        <v>238.15</v>
       </c>
       <c r="I21" t="n">
         <v>237.3810169966128</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>-5</v>
+        <v>-5.82</v>
       </c>
       <c r="L21" t="n">
-        <v>5.38</v>
+        <v>6.53</v>
       </c>
       <c r="M21" t="n">
         <v>1.13</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.84</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43049.38541666666</v>
+        <v>43052.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>264.75</v>
+        <v>255.95</v>
       </c>
       <c r="I22" t="n">
         <v>257.850549102038</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K22" t="n">
-        <v>11.17</v>
+        <v>7.47</v>
       </c>
       <c r="L22" t="n">
         <v>3.07</v>
       </c>
       <c r="M22" t="n">
-        <v>1.22</v>
+        <v>2.87</v>
       </c>
       <c r="N22" t="n">
-        <v>2.27</v>
+        <v>3.32</v>
       </c>
       <c r="O22" t="n">
         <v>0.78</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43104.38541666666</v>
+        <v>43105.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>258.6</v>
+        <v>259.5</v>
       </c>
       <c r="I23" t="n">
         <v>258.6710651039428</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.04</v>
+        <v>-1.39</v>
       </c>
       <c r="L23" t="n">
         <v>2.62</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43117.38541666666</v>
+        <v>43118.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>270.85</v>
+        <v>263.5</v>
       </c>
       <c r="I24" t="n">
         <v>267.9039411110517</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K24" t="n">
-        <v>4.37</v>
+        <v>1.54</v>
       </c>
       <c r="L24" t="n">
         <v>0.27</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.08</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43145.38541666666</v>
+        <v>43146.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>285.75</v>
+        <v>286.85</v>
       </c>
       <c r="I25" t="n">
         <v>286.6251840633351</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.44</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>9.34</v>
+        <v>10.17</v>
       </c>
       <c r="M25" t="n">
         <v>1.23</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43174.38541666666</v>
+        <v>43175.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>275.1</v>
+        <v>259</v>
       </c>
       <c r="I26" t="n">
         <v>268.0767096800129</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.1</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>5.87</v>
+        <v>10.35</v>
       </c>
       <c r="M26" t="n">
-        <v>1.31</v>
+        <v>5.14</v>
       </c>
       <c r="N26" t="n">
-        <v>2.27</v>
+        <v>5.85</v>
       </c>
       <c r="O26" t="n">
         <v>0.38</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>9.57</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43209.38541666666</v>
+        <v>43210.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>263.65</v>
+        <v>271.9</v>
       </c>
       <c r="I27" t="n">
         <v>271.1556263159811</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.8</v>
+        <v>-4.98</v>
       </c>
       <c r="L27" t="n">
-        <v>4.38</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
         <v>0.98</v>
       </c>
       <c r="N27" t="n">
-        <v>2.57</v>
+        <v>3.13</v>
       </c>
       <c r="O27" t="n">
         <v>-5.85</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43223.38541666666</v>
+        <v>43224.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>257.8</v>
+        <v>252.55</v>
       </c>
       <c r="I28" t="n">
         <v>253.5117140698086</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.19</v>
+        <v>-7.12</v>
       </c>
       <c r="L28" t="n">
-        <v>5.46</v>
+        <v>7.41</v>
       </c>
       <c r="M28" t="n">
         <v>0.79</v>
       </c>
       <c r="N28" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>3.13</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.98</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43243.38541666666</v>
+        <v>43244.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>257.15</v>
+        <v>260.75</v>
       </c>
       <c r="I29" t="n">
         <v>260.6511526306149</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.82</v>
+        <v>-3.25</v>
       </c>
       <c r="L29" t="n">
-        <v>3.19</v>
+        <v>3.76</v>
       </c>
       <c r="M29" t="n">
         <v>0.98</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.19</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43271.38541666666</v>
+        <v>43272.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>251.9</v>
+        <v>249.2</v>
       </c>
       <c r="I30" t="n">
         <v>250.1983359124392</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.39</v>
+        <v>-4.43</v>
       </c>
       <c r="L30" t="n">
-        <v>4.53</v>
+        <v>4.93</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.01</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43315.38541666666</v>
+        <v>43318.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>259.95</v>
+        <v>263.6</v>
       </c>
       <c r="I31" t="n">
         <v>260.6934559534192</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.31</v>
+        <v>-5.78</v>
       </c>
       <c r="L31" t="n">
-        <v>5.48</v>
+        <v>6.7</v>
       </c>
       <c r="M31" t="n">
         <v>1.43</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.4</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43368.38541666666</v>
+        <v>43369.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>256.25</v>
+        <v>253.75</v>
       </c>
       <c r="I32" t="n">
         <v>254.1381278228399</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.79</v>
+        <v>-3.74</v>
       </c>
       <c r="L32" t="n">
         <v>5.12</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H33" t="n">
-        <v>212.55</v>
+        <v>216.6</v>
       </c>
       <c r="I33" t="n">
         <v>213.7742723407378</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>154.6145833333333</v>
+        <v>155.6145833333333</v>
       </c>
       <c r="K33" t="n">
-        <v>16.24</v>
+        <v>14.64</v>
       </c>
       <c r="L33" t="n">
         <v>6.09</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.6</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43599</v>
+        <v>43600</v>
       </c>
       <c r="H34" t="n">
-        <v>225.1</v>
+        <v>218.85</v>
       </c>
       <c r="I34" t="n">
         <v>223.2891006422472</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K34" t="n">
-        <v>3.92</v>
+        <v>1.04</v>
       </c>
       <c r="L34" t="n">
         <v>2.61</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>8.69</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43614</v>
+        <v>43615</v>
       </c>
       <c r="H35" t="n">
-        <v>233.4</v>
+        <v>235.45</v>
       </c>
       <c r="I35" t="n">
         <v>233.7668339573434</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.65</v>
+        <v>-7.59</v>
       </c>
       <c r="L35" t="n">
-        <v>7.11</v>
+        <v>8.57</v>
       </c>
       <c r="M35" t="n">
         <v>2.43</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.03</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43650</v>
+        <v>43651</v>
       </c>
       <c r="H36" t="n">
-        <v>233.75</v>
+        <v>225.2</v>
       </c>
       <c r="I36" t="n">
         <v>230.761202819408</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.72</v>
+        <v>-4.35</v>
       </c>
       <c r="L36" t="n">
-        <v>2.31</v>
+        <v>4.78</v>
       </c>
       <c r="M36" t="n">
         <v>0.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>3.66</v>
       </c>
       <c r="O36" t="n">
         <v>0.88</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43733</v>
+        <v>43734</v>
       </c>
       <c r="H37" t="n">
-        <v>179.3</v>
+        <v>189.25</v>
       </c>
       <c r="I37" t="n">
         <v>189.030130506236</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
-        <v>20.38</v>
+        <v>15.96</v>
       </c>
       <c r="L37" t="n">
         <v>4.66</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>15.05</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H38" t="n">
-        <v>182.85</v>
+        <v>178.75</v>
       </c>
       <c r="I38" t="n">
         <v>180.8976418052753</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.38</v>
+        <v>-5.55</v>
       </c>
       <c r="L38" t="n">
         <v>10.41</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>9.34</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43825</v>
+        <v>43826</v>
       </c>
       <c r="H39" t="n">
-        <v>183.65</v>
+        <v>189.45</v>
       </c>
       <c r="I39" t="n">
         <v>188.3532058015527</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.74</v>
+        <v>-5.99</v>
       </c>
       <c r="L39" t="n">
-        <v>5.57</v>
+        <v>7.02</v>
       </c>
       <c r="M39" t="n">
         <v>0.82</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H40" t="n">
-        <v>188.2</v>
+        <v>178.65</v>
       </c>
       <c r="I40" t="n">
         <v>182.6317447541452</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.66</v>
+        <v>-5.7</v>
       </c>
       <c r="L40" t="n">
-        <v>3.04</v>
+        <v>6.15</v>
       </c>
       <c r="M40" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="N40" t="n">
-        <v>3.23</v>
+        <v>5.07</v>
       </c>
       <c r="O40" t="n">
         <v>3.16</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.44</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H41" t="n">
-        <v>124.65</v>
+        <v>131.55</v>
       </c>
       <c r="I41" t="n">
         <v>129.180214030183</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K41" t="n">
-        <v>30.23</v>
+        <v>26.36</v>
       </c>
       <c r="L41" t="n">
         <v>3.89</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>14.19</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43997</v>
+        <v>43998</v>
       </c>
       <c r="H42" t="n">
-        <v>122.95</v>
+        <v>122.1</v>
       </c>
       <c r="I42" t="n">
         <v>122.1342289118016</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.54</v>
+        <v>-7.18</v>
       </c>
       <c r="L42" t="n">
-        <v>7.64</v>
+        <v>8.32</v>
       </c>
       <c r="M42" t="n">
         <v>3.35</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.47</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44062</v>
+        <v>44063</v>
       </c>
       <c r="H43" t="n">
-        <v>125.8</v>
+        <v>128.95</v>
       </c>
       <c r="I43" t="n">
         <v>127.3564788499491</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.03</v>
+        <v>-5.61</v>
       </c>
       <c r="L43" t="n">
         <v>11.88</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.91</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44078</v>
+        <v>44081</v>
       </c>
       <c r="H44" t="n">
-        <v>123.3</v>
+        <v>122.8</v>
       </c>
       <c r="I44" t="n">
         <v>123.1673080179095</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.38</v>
+        <v>-4.77</v>
       </c>
       <c r="L44" t="n">
         <v>5.66</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.19</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44140</v>
+        <v>44141</v>
       </c>
       <c r="H45" t="n">
-        <v>111.6</v>
+        <v>113.4</v>
       </c>
       <c r="I45" t="n">
         <v>111.8301378581851</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K45" t="n">
-        <v>9.119999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="L45" t="n">
         <v>1.43</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H46" t="n">
-        <v>131.95</v>
+        <v>123.75</v>
       </c>
       <c r="I46" t="n">
         <v>123.9678350173571</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K46" t="n">
-        <v>16.36</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>2.91</v>
@@ -3063,7 +3614,7 @@
         <v>5.07</v>
       </c>
       <c r="N46" t="n">
-        <v>4.86</v>
+        <v>6.21</v>
       </c>
       <c r="O46" t="n">
         <v>1.61</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.44</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44207</v>
+        <v>44208</v>
       </c>
       <c r="H47" t="n">
-        <v>131.95</v>
+        <v>136.5</v>
       </c>
       <c r="I47" t="n">
         <v>136.1862061300441</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.63</v>
+        <v>-10.3</v>
       </c>
       <c r="L47" t="n">
-        <v>7.6</v>
+        <v>11.03</v>
       </c>
       <c r="M47" t="n">
         <v>2.68</v>
       </c>
       <c r="N47" t="n">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>-6.21</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H48" t="n">
-        <v>127.9</v>
+        <v>124</v>
       </c>
       <c r="I48" t="n">
         <v>125.6310327280432</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.3</v>
+        <v>-9.16</v>
       </c>
       <c r="L48" t="n">
-        <v>6.89</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N48" t="n">
         <v>3.19</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.3</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H49" t="n">
-        <v>127.8</v>
+        <v>133.7</v>
       </c>
       <c r="I49" t="n">
         <v>130.2433913694389</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.06</v>
+        <v>-7.82</v>
       </c>
       <c r="L49" t="n">
-        <v>3.59</v>
+        <v>8.27</v>
       </c>
       <c r="M49" t="n">
         <v>1.54</v>
       </c>
       <c r="N49" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="O49" t="n">
         <v>-3.05</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H50" t="n">
-        <v>130.15</v>
+        <v>127.6</v>
       </c>
       <c r="I50" t="n">
         <v>129.1971267536092</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.66</v>
+        <v>-4.56</v>
       </c>
       <c r="L50" t="n">
         <v>8.119999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>12.53</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44322</v>
+        <v>44323</v>
       </c>
       <c r="H51" t="n">
-        <v>125.3</v>
+        <v>127.4</v>
       </c>
       <c r="I51" t="n">
         <v>125.6288112946246</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>1.8</v>
+        <v>0.16</v>
       </c>
       <c r="L51" t="n">
         <v>3.41</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.02</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H52" t="n">
-        <v>141.65</v>
+        <v>136.3</v>
       </c>
       <c r="I52" t="n">
         <v>136.4830348807188</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K52" t="n">
-        <v>11.19</v>
+        <v>6.99</v>
       </c>
       <c r="L52" t="n">
         <v>1.33</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.89</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H53" t="n">
-        <v>133.7</v>
+        <v>135.75</v>
       </c>
       <c r="I53" t="n">
         <v>134.3067740398116</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K53" t="n">
-        <v>1.91</v>
+        <v>0.4</v>
       </c>
       <c r="L53" t="n">
         <v>5.03</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.51</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H54" t="n">
-        <v>163.75</v>
+        <v>162.05</v>
       </c>
       <c r="I54" t="n">
         <v>162.2054702366495</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K54" t="n">
-        <v>20.63</v>
+        <v>19.37</v>
       </c>
       <c r="L54" t="n">
         <v>3.17</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.61</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44567</v>
+        <v>44568</v>
       </c>
       <c r="H55" t="n">
-        <v>143.95</v>
+        <v>146.1</v>
       </c>
       <c r="I55" t="n">
         <v>144.6788999799136</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K55" t="n">
-        <v>11.17</v>
+        <v>9.84</v>
       </c>
       <c r="L55" t="n">
         <v>1.85</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.81</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H56" t="n">
-        <v>147.55</v>
+        <v>139.6</v>
       </c>
       <c r="I56" t="n">
         <v>143.2179521354772</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K56" t="n">
-        <v>0.99</v>
+        <v>-4.45</v>
       </c>
       <c r="L56" t="n">
-        <v>1.68</v>
+        <v>5.07</v>
       </c>
       <c r="M56" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="N56" t="n">
-        <v>3.81</v>
+        <v>5.39</v>
       </c>
       <c r="O56" t="n">
         <v>1.49</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>12.55</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44617</v>
+        <v>44620</v>
       </c>
       <c r="H57" t="n">
-        <v>152.2</v>
+        <v>157.8</v>
       </c>
       <c r="I57" t="n">
         <v>157.1230138853987</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
-        <v>-9.029999999999999</v>
+        <v>-13.04</v>
       </c>
       <c r="L57" t="n">
-        <v>9.960000000000001</v>
+        <v>13.32</v>
       </c>
       <c r="M57" t="n">
         <v>1.5</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>14.16</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H58" t="n">
-        <v>170.4</v>
+        <v>158.3</v>
       </c>
       <c r="I58" t="n">
         <v>169.8620692683151</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K58" t="n">
-        <v>7.98</v>
+        <v>0.32</v>
       </c>
       <c r="L58" t="n">
         <v>5.29</v>
@@ -3747,7 +4442,7 @@
         <v>1.41</v>
       </c>
       <c r="N58" t="n">
-        <v>6.77</v>
+        <v>7.1</v>
       </c>
       <c r="O58" t="n">
         <v>3.68</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>17.88</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H59" t="n">
-        <v>174.3</v>
+        <v>179.6</v>
       </c>
       <c r="I59" t="n">
         <v>177.7233798253482</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.11</v>
+        <v>-13.46</v>
       </c>
       <c r="L59" t="n">
-        <v>10.96</v>
+        <v>14.81</v>
       </c>
       <c r="M59" t="n">
         <v>1.81</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>12.61</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H60" t="n">
-        <v>176.9</v>
+        <v>167.45</v>
       </c>
       <c r="I60" t="n">
         <v>168.2936415745343</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.5</v>
+        <v>-6.77</v>
       </c>
       <c r="L60" t="n">
-        <v>3.98</v>
+        <v>7.15</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>3.76</v>
+        <v>5.34</v>
       </c>
       <c r="O60" t="n">
         <v>3.04</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>14.38</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H61" t="n">
-        <v>182.05</v>
+        <v>184.55</v>
       </c>
       <c r="I61" t="n">
         <v>183.9212200188979</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.720000000000001</v>
+        <v>-10.21</v>
       </c>
       <c r="L61" t="n">
-        <v>9.470000000000001</v>
+        <v>10.96</v>
       </c>
       <c r="M61" t="n">
         <v>1.95</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H62" t="n">
-        <v>207.5</v>
+        <v>200.6</v>
       </c>
       <c r="I62" t="n">
         <v>205.9730632694948</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K62" t="n">
-        <v>12.44</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>2.14</v>
@@ -3975,7 +4718,7 @@
         <v>3.71</v>
       </c>
       <c r="N62" t="n">
-        <v>2.58</v>
+        <v>3.33</v>
       </c>
       <c r="O62" t="n">
         <v>1.37</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H63" t="n">
-        <v>207.8</v>
+        <v>217.35</v>
       </c>
       <c r="I63" t="n">
         <v>213.0114093421439</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.59</v>
+        <v>-8.35</v>
       </c>
       <c r="L63" t="n">
-        <v>3.96</v>
+        <v>8.65</v>
       </c>
       <c r="M63" t="n">
         <v>1.57</v>
       </c>
       <c r="N63" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="O63" t="n">
         <v>-3.33</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.4</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>44879</v>
+        <v>44880</v>
       </c>
       <c r="H64" t="n">
-        <v>230.1</v>
+        <v>216.1</v>
       </c>
       <c r="I64" t="n">
         <v>224.0544772268169</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K64" t="n">
-        <v>5.87</v>
+        <v>-0.58</v>
       </c>
       <c r="L64" t="n">
         <v>4.05</v>
       </c>
       <c r="M64" t="n">
-        <v>1.19</v>
+        <v>5.17</v>
       </c>
       <c r="N64" t="n">
-        <v>2.4</v>
+        <v>6.08</v>
       </c>
       <c r="O64" t="n">
         <v>4.6</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>11.07</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>44945</v>
+        <v>44946</v>
       </c>
       <c r="H65" t="n">
-        <v>208.5</v>
+        <v>211.3</v>
       </c>
       <c r="I65" t="n">
         <v>210.6948273445135</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K65" t="n">
-        <v>3.52</v>
+        <v>2.22</v>
       </c>
       <c r="L65" t="n">
         <v>2.89</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.12</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>44965</v>
+        <v>44966</v>
       </c>
       <c r="H66" t="n">
-        <v>200.6</v>
+        <v>199.75</v>
       </c>
       <c r="I66" t="n">
         <v>200.0711554013382</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.06</v>
+        <v>-5.47</v>
       </c>
       <c r="L66" t="n">
-        <v>5.66</v>
+        <v>6.08</v>
       </c>
       <c r="M66" t="n">
         <v>2.22</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.79</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H67" t="n">
-        <v>204.95</v>
+        <v>207.15</v>
       </c>
       <c r="I67" t="n">
         <v>206.3341874918607</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.6</v>
+        <v>-3.7</v>
       </c>
       <c r="L67" t="n">
         <v>5.78</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.15</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45077</v>
+        <v>45078</v>
       </c>
       <c r="H68" t="n">
-        <v>224.55</v>
+        <v>214.45</v>
       </c>
       <c r="I68" t="n">
         <v>216.7402717796269</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K68" t="n">
-        <v>8.4</v>
+        <v>3.52</v>
       </c>
       <c r="L68" t="n">
         <v>0.99</v>
       </c>
       <c r="M68" t="n">
-        <v>2.06</v>
+        <v>4.48</v>
       </c>
       <c r="N68" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>1.07</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>7.01</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="H69" t="n">
-        <v>215.4</v>
+        <v>218.4</v>
       </c>
       <c r="I69" t="n">
         <v>217.9383661297194</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.44</v>
+        <v>-1.84</v>
       </c>
       <c r="L69" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="M69" t="n">
         <v>0.91</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.81</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H70" t="n">
-        <v>421.9</v>
+        <v>391.65</v>
       </c>
       <c r="I70" t="n">
         <v>403.1338001861833</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K70" t="n">
-        <v>93.18000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="L70" t="n">
         <v>3.3</v>
@@ -4431,7 +5270,7 @@
         <v>2.83</v>
       </c>
       <c r="N70" t="n">
-        <v>5.9</v>
+        <v>7.17</v>
       </c>
       <c r="O70" t="n">
         <v>1.39</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>9</v>
+      </c>
+      <c r="U70" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>14.24</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="H71" t="n">
-        <v>426.2</v>
+        <v>445.65</v>
       </c>
       <c r="I71" t="n">
         <v>434.4914791856269</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.82</v>
+        <v>-13.79</v>
       </c>
       <c r="L71" t="n">
-        <v>11.12</v>
+        <v>14.08</v>
       </c>
       <c r="M71" t="n">
         <v>1.3</v>
       </c>
       <c r="N71" t="n">
-        <v>3.77</v>
+        <v>4.56</v>
       </c>
       <c r="O71" t="n">
         <v>-7.17</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>10.05</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H72" t="n">
-        <v>481.1</v>
+        <v>414.95</v>
       </c>
       <c r="I72" t="n">
         <v>440.8762603147568</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K72" t="n">
-        <v>7.95</v>
+        <v>-6.89</v>
       </c>
       <c r="L72" t="n">
-        <v>8.4</v>
+        <v>13.44</v>
       </c>
       <c r="M72" t="n">
         <v>1.14</v>
       </c>
       <c r="N72" t="n">
-        <v>4.52</v>
+        <v>13.75</v>
       </c>
       <c r="O72" t="n">
         <v>4.56</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>20.93</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45488</v>
+        <v>45489</v>
       </c>
       <c r="H73" t="n">
-        <v>467.4</v>
+        <v>481.2</v>
       </c>
       <c r="I73" t="n">
         <v>476.3239004494394</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K73" t="n">
-        <v>-12.64</v>
+        <v>-15.97</v>
       </c>
       <c r="L73" t="n">
-        <v>15.95</v>
+        <v>17.32</v>
       </c>
       <c r="M73" t="n">
         <v>2.29</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.15</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H74" t="n">
-        <v>472.95</v>
+        <v>466.7</v>
       </c>
       <c r="I74" t="n">
         <v>468.278906710199</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.71</v>
+        <v>-3.01</v>
       </c>
       <c r="L74" t="n">
         <v>9.34</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.67</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H75" t="n">
-        <v>374.9</v>
+        <v>385.45</v>
       </c>
       <c r="I75" t="n">
         <v>382.2544708066928</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K75" t="n">
-        <v>19.67</v>
+        <v>17.41</v>
       </c>
       <c r="L75" t="n">
         <v>4.19</v>
@@ -4716,7 +5615,7 @@
         <v>2.06</v>
       </c>
       <c r="N75" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="O75" t="n">
         <v>-1.32</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>6</v>
+      </c>
+      <c r="U75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>11.01</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H76" t="n">
-        <v>374.9</v>
+        <v>367.55</v>
       </c>
       <c r="I76" t="n">
         <v>368.6702853799242</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.74</v>
+        <v>-4.64</v>
       </c>
       <c r="L76" t="n">
         <v>11.78</v>
       </c>
       <c r="M76" t="n">
-        <v>1.44</v>
+        <v>6.8</v>
       </c>
       <c r="N76" t="n">
         <v>3.1</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.67</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="H77" t="n">
-        <v>384.75</v>
+        <v>392.45</v>
       </c>
       <c r="I77" t="n">
         <v>392.0577974893902</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.68</v>
+        <v>-6.77</v>
       </c>
       <c r="L77" t="n">
         <v>7.55</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H78" t="n">
-        <v>373.9</v>
+        <v>370.9</v>
       </c>
       <c r="I78" t="n">
         <v>371.8045512881781</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K78" t="n">
-        <v>-4.73</v>
+        <v>-5.49</v>
       </c>
       <c r="L78" t="n">
-        <v>5.16</v>
+        <v>5.58</v>
       </c>
       <c r="M78" t="n">
         <v>0.6899999999999999</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>4.54</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="H79" t="n">
-        <v>379.5</v>
+        <v>381.1</v>
       </c>
       <c r="I79" t="n">
         <v>379.7401819504256</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.32</v>
+        <v>-2.75</v>
       </c>
       <c r="L79" t="n">
         <v>3.24</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>5.7</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H80" t="n">
-        <v>373.25</v>
+        <v>371.85</v>
       </c>
       <c r="I80" t="n">
         <v>373.2152798629696</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.06</v>
+        <v>-2.43</v>
       </c>
       <c r="L80" t="n">
-        <v>2.53</v>
+        <v>2.93</v>
       </c>
       <c r="M80" t="n">
         <v>0.21</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>4.22</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H81" t="n">
-        <v>386.95</v>
+        <v>387.85</v>
       </c>
       <c r="I81" t="n">
         <v>387.5372255754219</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K81" t="n">
-        <v>-4.06</v>
+        <v>-4.3</v>
       </c>
       <c r="L81" t="n">
-        <v>4.54</v>
+        <v>4.67</v>
       </c>
       <c r="M81" t="n">
         <v>0.64</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>4.21</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="H82" t="n">
-        <v>372.55</v>
+        <v>370.05</v>
       </c>
       <c r="I82" t="n">
         <v>371.5246969378749</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K82" t="n">
-        <v>-3.94</v>
+        <v>-4.59</v>
       </c>
       <c r="L82" t="n">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="M82" t="n">
         <v>0.43</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>4.4</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="H83" t="n">
-        <v>386.25</v>
+        <v>400.4</v>
       </c>
       <c r="I83" t="n">
         <v>386.3371085096388</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K83" t="n">
-        <v>-4.38</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>4.68</v>
+        <v>8.35</v>
       </c>
       <c r="M83" t="n">
         <v>0.49</v>
       </c>
       <c r="N83" t="n">
-        <v>1.97</v>
+        <v>3.66</v>
       </c>
       <c r="O83" t="n">
         <v>-0.67</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,25 +6215,25 @@
         <v>5.89</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="H84" t="n">
-        <v>419.15</v>
+        <v>408.95</v>
       </c>
       <c r="I84" t="n">
         <v>415.2036584764475</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K84" t="n">
-        <v>4.68</v>
+        <v>2.14</v>
       </c>
       <c r="L84" t="n">
         <v>3.48</v>
       </c>
       <c r="M84" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="N84" t="n">
         <v>4.81</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5265,25 +6284,25 @@
         <v>9.18</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H85" t="n">
-        <v>435.15</v>
+        <v>449.4</v>
       </c>
       <c r="I85" t="n">
         <v>446.4809642296213</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>-6.41</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>7.51</v>
+        <v>12.12</v>
       </c>
       <c r="M85" t="n">
-        <v>0.58</v>
+        <v>1.15</v>
       </c>
       <c r="N85" t="n">
         <v>3.31</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>8.02</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H86" t="n">
-        <v>451</v>
+        <v>446.2</v>
       </c>
       <c r="I86" t="n">
         <v>446.4990037697562</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K86" t="n">
-        <v>0.36</v>
+        <v>-0.71</v>
       </c>
       <c r="L86" t="n">
         <v>4.87</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>4</v>
+      </c>
+      <c r="U86" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -5379,28 +6422,28 @@
         <v>9.32</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H87" t="n">
-        <v>401.6</v>
+        <v>417.85</v>
       </c>
       <c r="I87" t="n">
         <v>417.8081272807613</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K87" t="n">
-        <v>10</v>
+        <v>6.35</v>
       </c>
       <c r="L87" t="n">
         <v>3.44</v>
       </c>
       <c r="M87" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="N87" t="n">
-        <v>2.17</v>
+        <v>4.05</v>
       </c>
       <c r="O87" t="n">
         <v>-1.06</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>4</v>
+      </c>
+      <c r="U87" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -5436,22 +6491,22 @@
         <v>6.4</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H88" t="n">
-        <v>411.55</v>
+        <v>404.8</v>
       </c>
       <c r="I88" t="n">
         <v>407.7521404691486</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.51</v>
+        <v>-3.12</v>
       </c>
       <c r="L88" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="M88" t="n">
         <v>0.89</v>
@@ -5466,7 +6521,19 @@
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5517,6 +6584,14 @@
       <c r="Q89" t="n">
         <v>12</v>
       </c>
+      <c r="R89" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10475,7 +11550,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.8</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="6">
@@ -10485,7 +11560,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10495,7 +11570,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -10505,7 +11580,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10515,7 +11590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -10525,7 +11600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77.2</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="11">
@@ -10535,7 +11610,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -10545,7 +11620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -10555,7 +11630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.6</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="14">
@@ -10565,7 +11640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.66</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="15">
@@ -10575,7 +11650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.93</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="16">
@@ -10585,7 +11660,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.36</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="17">
@@ -10595,7 +11670,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93.18000000000001</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="18">
@@ -10605,7 +11680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.9</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="19">
@@ -10615,7 +11690,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.32</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="20">
@@ -10625,7 +11700,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.54</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="21">
@@ -10635,7 +11710,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.95</v>
+        <v>17.32</v>
       </c>
     </row>
     <row r="22">
@@ -10645,7 +11720,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -10655,7 +11730,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -10665,7 +11740,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="25">
@@ -10685,7 +11760,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.61</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="27">
@@ -10695,7 +11770,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.029999999999999</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="28">
@@ -10705,7 +11780,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
